--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6968" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6968" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -818,6 +818,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -7775,7 +7779,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -7783,10 +7787,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7812,10 +7816,10 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7846,7 +7850,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7864,7 +7868,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7884,10 +7888,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7985,10 +7989,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8029,7 +8033,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -8088,10 +8092,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8191,10 +8195,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8294,10 +8298,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8397,10 +8401,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8500,10 +8504,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8601,10 +8605,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8702,10 +8706,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8805,10 +8809,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8908,10 +8912,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9011,10 +9015,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9037,13 +9041,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9094,7 +9098,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -9114,10 +9118,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9140,7 +9144,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -9173,7 +9177,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -9191,7 +9195,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9211,10 +9215,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9237,7 +9241,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -9290,7 +9294,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9310,10 +9314,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9336,13 +9340,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9373,7 +9377,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9391,7 +9395,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9411,10 +9415,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9440,10 +9444,10 @@
         <v>169</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9474,7 +9478,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9492,7 +9496,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9512,10 +9516,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9538,13 +9542,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9595,7 +9599,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9615,10 +9619,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9641,7 +9645,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9694,7 +9698,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9714,10 +9718,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9740,7 +9744,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9793,7 +9797,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9813,10 +9817,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9839,7 +9843,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9872,25 +9876,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9910,10 +9914,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9936,13 +9940,13 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9993,7 +9997,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10013,10 +10017,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10114,10 +10118,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10215,10 +10219,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10316,10 +10320,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10417,10 +10421,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10520,10 +10524,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10623,10 +10627,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10726,10 +10730,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10829,10 +10833,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10930,10 +10934,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10967,7 +10971,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>74</v>
@@ -10989,7 +10993,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -11007,7 +11011,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -11027,10 +11031,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11053,7 +11057,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -11106,7 +11110,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11126,10 +11130,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11152,7 +11156,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -11205,7 +11209,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11225,10 +11229,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11251,7 +11255,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11304,7 +11308,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11324,10 +11328,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11350,10 +11354,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -11405,7 +11409,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11425,10 +11429,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11451,10 +11455,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -11506,7 +11510,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11526,10 +11530,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11552,7 +11556,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11605,7 +11609,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11625,10 +11629,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11651,7 +11655,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11704,7 +11708,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11724,10 +11728,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11750,7 +11754,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11791,7 +11795,7 @@
         <v>74</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -11801,7 +11805,7 @@
         <v>124</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11821,13 +11825,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>74</v>
@@ -11849,10 +11853,10 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -11904,7 +11908,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11924,10 +11928,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12025,10 +12029,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12126,10 +12130,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12227,10 +12231,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12328,10 +12332,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12431,10 +12435,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12534,10 +12538,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12637,10 +12641,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12740,10 +12744,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12841,10 +12845,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12881,7 +12885,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -12900,7 +12904,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12918,7 +12922,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -12938,10 +12942,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12968,7 +12972,7 @@
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13019,7 +13023,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -13039,10 +13043,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13069,12 +13073,12 @@
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
@@ -13120,7 +13124,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13140,10 +13144,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13219,7 +13223,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13239,10 +13243,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13265,7 +13269,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13318,7 +13322,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13338,10 +13342,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13364,7 +13368,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13417,7 +13421,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13437,10 +13441,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13463,7 +13467,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13516,7 +13520,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13536,10 +13540,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13562,7 +13566,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13615,7 +13619,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13635,10 +13639,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13661,7 +13665,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13714,7 +13718,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13734,10 +13738,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13760,7 +13764,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13813,7 +13817,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13833,10 +13837,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13859,7 +13863,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13912,7 +13916,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13932,10 +13936,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13958,7 +13962,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -14011,7 +14015,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -14031,10 +14035,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14057,7 +14061,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -14110,7 +14114,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -14130,10 +14134,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14156,7 +14160,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14209,7 +14213,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14229,10 +14233,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14255,7 +14259,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14308,7 +14312,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14328,13 +14332,13 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>74</v>
@@ -14356,10 +14360,10 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -14411,7 +14415,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14431,10 +14435,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14532,10 +14536,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14633,10 +14637,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14734,10 +14738,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14835,10 +14839,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14938,10 +14942,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15041,10 +15045,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15144,10 +15148,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15247,10 +15251,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15348,10 +15352,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15388,7 +15392,7 @@
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15407,7 +15411,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15425,7 +15429,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -15445,10 +15449,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15475,7 +15479,7 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15526,7 +15530,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15546,10 +15550,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15576,12 +15580,12 @@
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
@@ -15627,7 +15631,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15647,10 +15651,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15726,7 +15730,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15746,10 +15750,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15772,7 +15776,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15825,7 +15829,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15845,10 +15849,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15871,7 +15875,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15924,7 +15928,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15944,10 +15948,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15970,7 +15974,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16023,7 +16027,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16043,10 +16047,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16069,7 +16073,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16122,7 +16126,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -16142,10 +16146,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16168,7 +16172,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16221,7 +16225,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16241,10 +16245,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16267,7 +16271,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16320,7 +16324,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16340,10 +16344,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16366,7 +16370,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16419,7 +16423,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16439,10 +16443,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16465,7 +16469,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16518,7 +16522,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16538,10 +16542,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16564,7 +16568,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16617,7 +16621,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16637,10 +16641,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16663,7 +16667,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16716,7 +16720,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16736,10 +16740,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16762,7 +16766,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16815,7 +16819,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16835,13 +16839,13 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>74</v>
@@ -16863,10 +16867,10 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -16918,7 +16922,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16938,10 +16942,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17039,10 +17043,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17140,10 +17144,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17241,10 +17245,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17342,10 +17346,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17445,10 +17449,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17548,10 +17552,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17651,10 +17655,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17754,10 +17758,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17855,10 +17859,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17895,7 +17899,7 @@
         <v>74</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>74</v>
@@ -17914,7 +17918,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -17932,7 +17936,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -17952,10 +17956,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17982,7 +17986,7 @@
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -18033,7 +18037,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18053,10 +18057,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18083,12 +18087,12 @@
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
@@ -18134,7 +18138,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18154,10 +18158,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18233,7 +18237,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18253,10 +18257,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18279,7 +18283,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18332,7 +18336,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18352,10 +18356,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18378,7 +18382,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18431,7 +18435,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18451,10 +18455,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18477,7 +18481,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18530,7 +18534,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18550,10 +18554,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18576,7 +18580,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18629,7 +18633,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18649,10 +18653,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18675,7 +18679,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18728,7 +18732,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18748,10 +18752,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18774,7 +18778,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18827,7 +18831,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18847,10 +18851,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18873,7 +18877,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18926,7 +18930,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18946,10 +18950,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18972,7 +18976,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19025,7 +19029,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19045,10 +19049,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19071,7 +19075,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19124,7 +19128,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -19144,10 +19148,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19170,7 +19174,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19223,7 +19227,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19243,10 +19247,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19269,7 +19273,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19322,7 +19326,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19342,13 +19346,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>74</v>
@@ -19370,10 +19374,10 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -19425,7 +19429,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19445,10 +19449,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19546,10 +19550,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19647,10 +19651,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19748,10 +19752,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19849,10 +19853,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19952,10 +19956,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20055,10 +20059,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20158,10 +20162,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20261,10 +20265,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20362,10 +20366,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20402,7 +20406,7 @@
         <v>74</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>74</v>
@@ -20421,7 +20425,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>74</v>
@@ -20439,7 +20443,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>75</v>
@@ -20459,10 +20463,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20489,7 +20493,7 @@
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20540,7 +20544,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20560,10 +20564,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20590,12 +20594,12 @@
       </c>
       <c r="L184" s="2"/>
       <c r="M184" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q184" s="2"/>
       <c r="R184" t="s" s="2">
@@ -20641,7 +20645,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20661,10 +20665,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20740,7 +20744,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20760,10 +20764,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20786,7 +20790,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -20839,7 +20843,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -20859,10 +20863,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20885,7 +20889,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -20938,7 +20942,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -20958,10 +20962,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -20984,7 +20988,7 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21037,7 +21041,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21057,10 +21061,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21083,7 +21087,7 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21136,7 +21140,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -21156,10 +21160,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21182,7 +21186,7 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21235,7 +21239,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -21255,10 +21259,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21281,7 +21285,7 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21334,7 +21338,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -21354,10 +21358,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21380,7 +21384,7 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21433,7 +21437,7 @@
         <v>74</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -21453,10 +21457,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21479,7 +21483,7 @@
         <v>74</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21532,7 +21536,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -21552,10 +21556,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21578,7 +21582,7 @@
         <v>74</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -21631,7 +21635,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -21651,10 +21655,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21677,7 +21681,7 @@
         <v>74</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21730,7 +21734,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -21750,10 +21754,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21776,7 +21780,7 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -21829,7 +21833,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -21849,13 +21853,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>74</v>
@@ -21877,10 +21881,10 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
@@ -21932,7 +21936,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -21952,10 +21956,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22053,10 +22057,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22154,10 +22158,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22255,10 +22259,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22356,10 +22360,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22459,10 +22463,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22562,10 +22566,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22665,10 +22669,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22768,10 +22772,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22869,10 +22873,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22909,7 +22913,7 @@
         <v>74</v>
       </c>
       <c r="S207" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T207" t="s" s="2">
         <v>74</v>
@@ -22928,7 +22932,7 @@
       </c>
       <c r="Y207" s="2"/>
       <c r="Z207" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>74</v>
@@ -22946,7 +22950,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>75</v>
@@ -22966,10 +22970,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -22996,7 +23000,7 @@
       </c>
       <c r="L208" s="2"/>
       <c r="M208" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -23047,7 +23051,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23067,10 +23071,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23097,12 +23101,12 @@
       </c>
       <c r="L209" s="2"/>
       <c r="M209" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q209" s="2"/>
       <c r="R209" t="s" s="2">
@@ -23148,7 +23152,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23168,10 +23172,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23247,7 +23251,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23267,10 +23271,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23293,7 +23297,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23346,7 +23350,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23366,10 +23370,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23392,7 +23396,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23445,7 +23449,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23465,10 +23469,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23491,7 +23495,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23544,7 +23548,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23564,10 +23568,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23590,7 +23594,7 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23643,7 +23647,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -23663,10 +23667,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23689,7 +23693,7 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23742,7 +23746,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -23762,10 +23766,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -23788,7 +23792,7 @@
         <v>74</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -23841,7 +23845,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -23861,10 +23865,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -23887,7 +23891,7 @@
         <v>74</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -23940,7 +23944,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -23960,10 +23964,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -23986,7 +23990,7 @@
         <v>74</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24039,7 +24043,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -24059,10 +24063,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24085,7 +24089,7 @@
         <v>74</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24138,7 +24142,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -24158,10 +24162,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24184,7 +24188,7 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24237,7 +24241,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -24257,10 +24261,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24283,7 +24287,7 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24336,7 +24340,7 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -24356,10 +24360,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24382,7 +24386,7 @@
         <v>74</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24435,7 +24439,7 @@
         <v>74</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -24455,10 +24459,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24481,7 +24485,7 @@
         <v>74</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24534,7 +24538,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -24554,10 +24558,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24580,7 +24584,7 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -24633,7 +24637,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
